--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text_1sthalf/lang_multi_text_1sthalf__story_dialogue__part_0003.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text_1sthalf/lang_multi_text_1sthalf__story_dialogue__part_0003.xlsx
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Đúng như cái tên của nó thôi. Nhưng... đừng tạo ra nó trừ khi sinh tử存亡.</t>
+          <t>Đúng như cái tên của nó thôi. Nhưng... đừng tạo ra nó trừ khi sinh tử tồn vong.</t>
         </is>
       </c>
     </row>
